--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>135935558</v>
       </c>
       <c r="B11" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -1686,7 +1686,7 @@
         <v>135935558</v>
       </c>
       <c r="B11" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,45 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133218929</v>
+        <v>136072078</v>
       </c>
       <c r="B2" t="n">
-        <v>97888</v>
+        <v>92290</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2604</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogsväg till St Örtjärn, Skogsväg till St Örtjärn, Hl</t>
+          <t>Granndalen Ost Övre, Granndalen Ost Övre, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334697</v>
+        <v>334596</v>
       </c>
       <c r="R2" t="n">
-        <v>6387285</v>
+        <v>6387222</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,30 +748,36 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>18:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gammal övervuxen granlåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,16 +795,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133218929</t>
+          <t>https://artportalen.se/Sighting/136072078</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133218532</v>
+        <v>133218929</v>
       </c>
       <c r="B3" t="n">
-        <v>91958</v>
+        <v>97888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4660</v>
+        <v>2604</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334686</v>
+        <v>334697</v>
       </c>
       <c r="R3" t="n">
-        <v>6387294</v>
+        <v>6387285</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,13 +907,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133218532</t>
+          <t>https://artportalen.se/Sighting/133218929</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133221543</v>
+        <v>133218532</v>
       </c>
       <c r="B4" t="n">
         <v>91958</v>
@@ -935,14 +944,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Berget Norr, Berget Norr, Hl</t>
+          <t>Skogsväg till St Örtjärn, Skogsväg till St Örtjärn, Hl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334847</v>
+        <v>334686</v>
       </c>
       <c r="R4" t="n">
-        <v>6387341</v>
+        <v>6387294</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,38 +1019,38 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133221543</t>
+          <t>https://artportalen.se/Sighting/133218532</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133220773</v>
+        <v>133221543</v>
       </c>
       <c r="B5" t="n">
-        <v>79992</v>
+        <v>91958</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>4660</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>334843</v>
+        <v>334847</v>
       </c>
       <c r="R5" t="n">
-        <v>6387321</v>
+        <v>6387341</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,13 +1131,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133220773</t>
+          <t>https://artportalen.se/Sighting/133221543</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133622754</v>
+        <v>133220773</v>
       </c>
       <c r="B6" t="n">
         <v>79992</v>
@@ -1157,19 +1166,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brännåsen-Granndalen, Hl</t>
+          <t>Berget Norr, Berget Norr, Hl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>334851</v>
+        <v>334843</v>
       </c>
       <c r="R6" t="n">
-        <v>6387262</v>
+        <v>6387321</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,12 +1202,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,31 +1226,30 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Mats Foss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Mats Foss</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133622754</t>
+          <t>https://artportalen.se/Sighting/133220773</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133622775</v>
+        <v>133622754</v>
       </c>
       <c r="B7" t="n">
         <v>79992</v>
@@ -1272,10 +1287,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>334889</v>
+        <v>334851</v>
       </c>
       <c r="R7" t="n">
-        <v>6387268</v>
+        <v>6387262</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,48 +1349,43 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133622775</t>
+          <t>https://artportalen.se/Sighting/133622754</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133622696</v>
+        <v>133622775</v>
       </c>
       <c r="B8" t="n">
-        <v>57972</v>
+        <v>79992</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1383,10 +1393,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>334807</v>
+        <v>334889</v>
       </c>
       <c r="R8" t="n">
-        <v>6387241</v>
+        <v>6387268</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,6 +1437,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1444,13 +1455,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133622696</t>
+          <t>https://artportalen.se/Sighting/133622775</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133622725</v>
+        <v>133622696</v>
       </c>
       <c r="B9" t="n">
         <v>57972</v>
@@ -1493,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>334851</v>
+        <v>334807</v>
       </c>
       <c r="R9" t="n">
-        <v>6387262</v>
+        <v>6387241</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,16 +1565,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133622725</t>
+          <t>https://artportalen.se/Sighting/133622696</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133623855</v>
+        <v>133622725</v>
       </c>
       <c r="B10" t="n">
-        <v>57153</v>
+        <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,16 +1582,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1588,22 +1599,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1611,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>334766</v>
+        <v>334851</v>
       </c>
       <c r="R10" t="n">
-        <v>6387298</v>
+        <v>6387262</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1649,11 +1652,6 @@
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>En tupp i sin hemvist respektive revir</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1677,16 +1675,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133623855</t>
+          <t>https://artportalen.se/Sighting/133622725</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135935558</v>
+        <v>133623855</v>
       </c>
       <c r="B11" t="n">
-        <v>98208</v>
+        <v>57153</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,34 +1692,50 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Granndalen, Granndalen, Hl</t>
+          <t>Brännåsen-Granndalen, Hl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>334547</v>
+        <v>334766</v>
       </c>
       <c r="R11" t="n">
-        <v>6387168</v>
+        <v>6387298</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1748,22 +1762,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:21</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:21</t>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>En tupp i sin hemvist respektive revir</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1778,18 +1787,247 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mats Foss</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mats Foss</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/133623855</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135935558</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98208</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Granndalen, Granndalen, Hl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>334547</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6387168</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mölndal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lindome</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135935558</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136071498</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98205</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Granndalen, Granndalen, Hl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>334542</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6387209</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mölndal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lindome</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136071498</t>
         </is>
       </c>
     </row>
@@ -1805,6 +2043,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1137,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133220773</v>
+        <v>136812310</v>
       </c>
       <c r="B6" t="n">
-        <v>79992</v>
+        <v>93447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,34 +1148,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Berget Norr, Berget Norr, Hl</t>
+          <t>Långebacke, Långebacke, Hl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>334843</v>
+        <v>334468</v>
       </c>
       <c r="R6" t="n">
-        <v>6387321</v>
+        <v>6387204</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,22 +1202,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,13 +1243,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133220773</t>
+          <t>https://artportalen.se/Sighting/136812310</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133622754</v>
+        <v>133220773</v>
       </c>
       <c r="B7" t="n">
         <v>79992</v>
@@ -1278,19 +1278,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brännåsen-Granndalen, Hl</t>
+          <t>Berget Norr, Berget Norr, Hl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>334851</v>
+        <v>334843</v>
       </c>
       <c r="R7" t="n">
-        <v>6387262</v>
+        <v>6387321</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,12 +1314,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,31 +1338,30 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Mats Foss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Mats Foss</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133622754</t>
+          <t>https://artportalen.se/Sighting/133220773</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133622775</v>
+        <v>133622754</v>
       </c>
       <c r="B8" t="n">
         <v>79992</v>
@@ -1393,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>334889</v>
+        <v>334851</v>
       </c>
       <c r="R8" t="n">
-        <v>6387268</v>
+        <v>6387262</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,48 +1461,43 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133622775</t>
+          <t>https://artportalen.se/Sighting/133622754</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133622696</v>
+        <v>133622775</v>
       </c>
       <c r="B9" t="n">
-        <v>57972</v>
+        <v>79992</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1504,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>334807</v>
+        <v>334889</v>
       </c>
       <c r="R9" t="n">
-        <v>6387241</v>
+        <v>6387268</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,6 +1549,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1565,13 +1567,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133622696</t>
+          <t>https://artportalen.se/Sighting/133622775</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133622725</v>
+        <v>133622696</v>
       </c>
       <c r="B10" t="n">
         <v>57972</v>
@@ -1614,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>334851</v>
+        <v>334807</v>
       </c>
       <c r="R10" t="n">
-        <v>6387262</v>
+        <v>6387241</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,16 +1677,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133622725</t>
+          <t>https://artportalen.se/Sighting/133622696</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133623855</v>
+        <v>133622725</v>
       </c>
       <c r="B11" t="n">
-        <v>57153</v>
+        <v>57972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1692,16 +1694,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1709,22 +1711,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1732,10 +1726,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>334766</v>
+        <v>334851</v>
       </c>
       <c r="R11" t="n">
-        <v>6387298</v>
+        <v>6387262</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,11 +1764,6 @@
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>En tupp i sin hemvist respektive revir</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1798,16 +1787,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133623855</t>
+          <t>https://artportalen.se/Sighting/133622725</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135935558</v>
+        <v>133623855</v>
       </c>
       <c r="B12" t="n">
-        <v>98208</v>
+        <v>57153</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,34 +1804,50 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Granndalen, Granndalen, Hl</t>
+          <t>Brännåsen-Granndalen, Hl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>334547</v>
+        <v>334766</v>
       </c>
       <c r="R12" t="n">
-        <v>6387168</v>
+        <v>6387298</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1869,22 +1874,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:21</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:21</t>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>En tupp i sin hemvist respektive revir</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,27 +1899,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mats Foss</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mats Foss</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135935558</t>
+          <t>https://artportalen.se/Sighting/133623855</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136071498</v>
+        <v>135935558</v>
       </c>
       <c r="B13" t="n">
-        <v>98205</v>
+        <v>98208</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,38 +1927,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>224361</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Granndalen, Granndalen, Hl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>334542</v>
+        <v>334547</v>
       </c>
       <c r="R13" t="n">
-        <v>6387209</v>
+        <v>6387168</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1985,22 +1981,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2009,7 +2005,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2026,6 +2021,123 @@
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135935558</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136071498</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98205</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Granndalen, Granndalen, Hl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>334542</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6387209</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mölndal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lindome</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136071498</t>
         </is>
@@ -2045,6 +2157,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136072078</v>
       </c>
       <c r="B2" t="n">
-        <v>92290</v>
+        <v>92292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>136812310</v>
       </c>
       <c r="B6" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>136071498</v>
       </c>
       <c r="B14" t="n">
-        <v>98205</v>
+        <v>98207</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1793,10 +1793,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133623855</v>
+        <v>136888553</v>
       </c>
       <c r="B12" t="n">
-        <v>57153</v>
+        <v>57195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1804,21 +1804,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1836,21 +1836,19 @@
           <t>hane</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Brännåsen-Granndalen, Hl</t>
+          <t>Granndalen Ost Övre, Granndalen Ost Övre, Hl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>334766</v>
+        <v>334747</v>
       </c>
       <c r="R12" t="n">
-        <v>6387298</v>
+        <v>6387144</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1874,17 +1872,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>En tupp i sin hemvist respektive revir</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,27 +1902,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Mats Foss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Mats Foss</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133623855</t>
+          <t>https://artportalen.se/Sighting/136888553</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135935558</v>
+        <v>133623855</v>
       </c>
       <c r="B13" t="n">
-        <v>98208</v>
+        <v>57153</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,34 +1930,50 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Granndalen, Granndalen, Hl</t>
+          <t>Brännåsen-Granndalen, Hl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>334547</v>
+        <v>334766</v>
       </c>
       <c r="R13" t="n">
-        <v>6387168</v>
+        <v>6387298</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1981,22 +2000,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:21</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:21</t>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>En tupp i sin hemvist respektive revir</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2011,27 +2025,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mats Foss</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mats Foss</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135935558</t>
+          <t>https://artportalen.se/Sighting/133623855</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136071498</v>
+        <v>135935558</v>
       </c>
       <c r="B14" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,38 +2053,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>224361</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Granndalen, Granndalen, Hl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>334542</v>
+        <v>334547</v>
       </c>
       <c r="R14" t="n">
-        <v>6387209</v>
+        <v>6387168</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2097,22 +2107,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2121,7 +2131,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2138,6 +2147,123 @@
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135935558</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136071498</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98207</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Granndalen, Granndalen, Hl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>334542</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6387209</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mölndal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lindome</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136071498</t>
         </is>
@@ -2158,6 +2284,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1573,56 +1573,72 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133622696</v>
+        <v>136891333</v>
       </c>
       <c r="B10" t="n">
-        <v>57972</v>
+        <v>57934</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100034</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blå kärrhök</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Circus cyaneus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+          <t>(Linnaeus, 1766)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Brännåsen-Granndalen, Hl</t>
+          <t>Granndalen Ost Övre, Granndalen Ost Övre, Hl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>334807</v>
+        <v>334747</v>
       </c>
       <c r="R10" t="n">
-        <v>6387241</v>
+        <v>6387144</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,12 +1662,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Flög förbi mossparti vid tjärnen samt jagade änder i mossen. Troligen sträckande fågel.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1666,24 +1697,24 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Mats Foss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Mats Foss</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133622696</t>
+          <t>https://artportalen.se/Sighting/136891333</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133622725</v>
+        <v>133622696</v>
       </c>
       <c r="B11" t="n">
         <v>57972</v>
@@ -1726,10 +1757,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>334851</v>
+        <v>334807</v>
       </c>
       <c r="R11" t="n">
-        <v>6387262</v>
+        <v>6387241</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1787,16 +1818,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133622725</t>
+          <t>https://artportalen.se/Sighting/133622696</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136888553</v>
+        <v>133622725</v>
       </c>
       <c r="B12" t="n">
-        <v>57195</v>
+        <v>57972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1804,51 +1835,45 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Granndalen Ost Övre, Granndalen Ost Övre, Hl</t>
+          <t>Brännåsen-Granndalen, Hl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>334747</v>
+        <v>334851</v>
       </c>
       <c r="R12" t="n">
-        <v>6387144</v>
+        <v>6387262</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1872,22 +1897,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:48</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:48</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,27 +1917,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mats Foss</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mats Foss</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136888553</t>
+          <t>https://artportalen.se/Sighting/133622725</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133623855</v>
+        <v>136888553</v>
       </c>
       <c r="B13" t="n">
-        <v>57153</v>
+        <v>57195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1930,21 +1945,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1962,21 +1977,19 @@
           <t>hane</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Brännåsen-Granndalen, Hl</t>
+          <t>Granndalen Ost Övre, Granndalen Ost Övre, Hl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>334766</v>
+        <v>334747</v>
       </c>
       <c r="R13" t="n">
-        <v>6387298</v>
+        <v>6387144</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2000,17 +2013,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>En tupp i sin hemvist respektive revir</t>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2025,27 +2043,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Mats Foss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Mats Foss</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133623855</t>
+          <t>https://artportalen.se/Sighting/136888553</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135935558</v>
+        <v>133623855</v>
       </c>
       <c r="B14" t="n">
-        <v>98208</v>
+        <v>57153</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2053,34 +2071,50 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Granndalen, Granndalen, Hl</t>
+          <t>Brännåsen-Granndalen, Hl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>334547</v>
+        <v>334766</v>
       </c>
       <c r="R14" t="n">
-        <v>6387168</v>
+        <v>6387298</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2107,22 +2141,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:21</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:21</t>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>En tupp i sin hemvist respektive revir</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2137,27 +2166,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mats Foss</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mats Foss</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135935558</t>
+          <t>https://artportalen.se/Sighting/133623855</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136071498</v>
+        <v>135935558</v>
       </c>
       <c r="B15" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2165,38 +2194,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>224361</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Granndalen, Granndalen, Hl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>334542</v>
+        <v>334547</v>
       </c>
       <c r="R15" t="n">
-        <v>6387209</v>
+        <v>6387168</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2223,22 +2248,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,7 +2272,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2264,6 +2288,123 @@
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135935558</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136071498</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98207</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Granndalen, Granndalen, Hl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>334542</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6387209</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mölndal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lindome</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136071498</t>
         </is>
@@ -2285,6 +2426,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136072078</v>
       </c>
       <c r="B2" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>136812310</v>
       </c>
       <c r="B6" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>136071498</v>
       </c>
       <c r="B16" t="n">
-        <v>98207</v>
+        <v>98213</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136072078</v>
       </c>
       <c r="B2" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>136812310</v>
       </c>
       <c r="B6" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>136071498</v>
       </c>
       <c r="B16" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136072078</v>
       </c>
       <c r="B2" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>136812310</v>
       </c>
       <c r="B6" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>136071498</v>
       </c>
       <c r="B16" t="n">
-        <v>98215</v>
+        <v>98216</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136072078</v>
       </c>
       <c r="B2" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>136812310</v>
       </c>
       <c r="B6" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>136071498</v>
       </c>
       <c r="B16" t="n">
-        <v>98216</v>
+        <v>98222</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136072078</v>
       </c>
       <c r="B2" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>136812310</v>
       </c>
       <c r="B6" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>136071498</v>
       </c>
       <c r="B16" t="n">
-        <v>98222</v>
+        <v>98226</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -2298,7 +2298,7 @@
         <v>136071498</v>
       </c>
       <c r="B16" t="n">
-        <v>98226</v>
+        <v>98228</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136072078</v>
       </c>
       <c r="B2" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>136812310</v>
       </c>
       <c r="B6" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>136071498</v>
       </c>
       <c r="B16" t="n">
-        <v>98228</v>
+        <v>98230</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136072078</v>
       </c>
       <c r="B2" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>136812310</v>
       </c>
       <c r="B6" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>136891333</v>
       </c>
       <c r="B10" t="n">
-        <v>57934</v>
+        <v>57947</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mats Foss</t>
+          <t>Mats Foss, Christina Sandblom</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1937,7 +1937,7 @@
         <v>136888553</v>
       </c>
       <c r="B13" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>136071498</v>
       </c>
       <c r="B16" t="n">
-        <v>98230</v>
+        <v>98243</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136072078</v>
       </c>
       <c r="B2" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>136812310</v>
       </c>
       <c r="B6" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>136891333</v>
       </c>
       <c r="B10" t="n">
-        <v>57947</v>
+        <v>57949</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>136888553</v>
       </c>
       <c r="B13" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>136071498</v>
       </c>
       <c r="B16" t="n">
-        <v>98243</v>
+        <v>98245</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -1606,21 +1606,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1967,16 +1955,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Granndalen Ost Övre, Granndalen Ost Övre, Hl</t>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136072078</v>
       </c>
       <c r="B2" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>136812310</v>
       </c>
       <c r="B6" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>136071498</v>
       </c>
       <c r="B16" t="n">
-        <v>98245</v>
+        <v>98248</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136072078</v>
       </c>
       <c r="B2" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>136812310</v>
       </c>
       <c r="B6" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>136891333</v>
       </c>
       <c r="B10" t="n">
-        <v>57949</v>
+        <v>57959</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136888553</v>
       </c>
       <c r="B13" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>136071498</v>
       </c>
       <c r="B16" t="n">
-        <v>98248</v>
+        <v>98258</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136072078</v>
       </c>
       <c r="B2" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>136812310</v>
       </c>
       <c r="B6" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>136071498</v>
       </c>
       <c r="B16" t="n">
-        <v>98258</v>
+        <v>98259</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136072078</v>
       </c>
       <c r="B2" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>136812310</v>
       </c>
       <c r="B6" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>136891333</v>
       </c>
       <c r="B10" t="n">
-        <v>57959</v>
+        <v>57960</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>136888553</v>
       </c>
       <c r="B13" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>136071498</v>
       </c>
       <c r="B16" t="n">
-        <v>98259</v>
+        <v>98264</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136072078</v>
       </c>
       <c r="B2" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>136812310</v>
       </c>
       <c r="B6" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>136071498</v>
       </c>
       <c r="B16" t="n">
-        <v>98264</v>
+        <v>98266</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136072078</v>
       </c>
       <c r="B2" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>136812310</v>
       </c>
       <c r="B6" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>136891333</v>
       </c>
       <c r="B10" t="n">
-        <v>57960</v>
+        <v>57961</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>136071498</v>
       </c>
       <c r="B16" t="n">
-        <v>98266</v>
+        <v>98272</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 31321-2025 artfynd.xlsx
+++ b/artfynd/A 31321-2025 artfynd.xlsx
@@ -1576,7 +1576,7 @@
         <v>136891333</v>
       </c>
       <c r="B10" t="n">
-        <v>57961</v>
+        <v>57964</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
